--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2018/MASSACHUSETTS_2018.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2018/MASSACHUSETTS_2018.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D310"/>
+  <dimension ref="A1:D304"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Mexicali</t>
@@ -408,6 +413,11 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>Tijuana</t>
@@ -421,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Total</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Acapetahua</t>
@@ -496,9 +521,14 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Amatenango de la Frontera</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C10">
@@ -509,9 +539,14 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bejucal de Ocampo</t>
+          <t>Bejucal De Ocampo</t>
         </is>
       </c>
       <c r="C11">
@@ -522,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Cacahoatán</t>
@@ -535,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Chamula</t>
@@ -548,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Chapultenango</t>
@@ -561,9 +611,14 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Comitán de Domínguez</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C15">
@@ -574,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>El Porvenir</t>
@@ -587,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Frontera Comalapa</t>
@@ -600,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Frontera Hidalgo</t>
@@ -613,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Huehuetán</t>
@@ -626,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Huixtán</t>
@@ -639,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Huixtla</t>
@@ -652,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -665,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>La Concordia</t>
@@ -678,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>La Grandeza</t>
@@ -691,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>La Trinitaria</t>
@@ -704,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Mapastepec</t>
@@ -717,9 +827,14 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mazapa de Madero</t>
+          <t>Mazapa De Madero</t>
         </is>
       </c>
       <c r="C27">
@@ -730,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Motozintla</t>
@@ -743,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Ocosingo</t>
@@ -756,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Palenque</t>
@@ -769,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Pantelhó</t>
@@ -782,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Pijijiapan</t>
@@ -795,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Sabanilla</t>
@@ -808,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Siltepec</t>
@@ -821,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Suchiate</t>
@@ -834,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -847,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Tenejapa</t>
@@ -860,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Tonalá</t>
@@ -873,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Tuxtla Chico</t>
@@ -886,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Tuzantán</t>
@@ -899,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Unión Juárez</t>
@@ -912,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Villa Comaltitlán</t>
@@ -925,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Villa Corzo</t>
@@ -938,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Villaflores</t>
@@ -951,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Total</t>
@@ -982,9 +1187,14 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C47">
@@ -995,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1010,7 +1225,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1026,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -1039,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -1052,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1065,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -1078,6 +1313,11 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -1091,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -1104,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1117,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Milpa Alta</t>
@@ -1130,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Tláhuac</t>
@@ -1143,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1156,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1187,9 +1457,14 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>San Juan de Guadalupe</t>
+          <t>San Juan De Guadalupe</t>
         </is>
       </c>
       <c r="C62">
@@ -1200,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1215,12 +1495,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Acambay de Ruíz Castañeda</t>
+          <t>Acambay De Ruíz Castañeda</t>
         </is>
       </c>
       <c r="C64">
@@ -1231,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Amatepec</t>
@@ -1244,9 +1529,14 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Atizapán de Zaragoza</t>
+          <t>Atizapán De Zaragoza</t>
         </is>
       </c>
       <c r="C66">
@@ -1257,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Chicoloapan</t>
@@ -1270,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Cuautitlán</t>
@@ -1283,9 +1583,14 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C69">
@@ -1296,9 +1601,14 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ixtapan de la Sal</t>
+          <t>Ixtapan De La Sal</t>
         </is>
       </c>
       <c r="C70">
@@ -1309,9 +1619,14 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ixtapan del Oro</t>
+          <t>Ixtapan Del Oro</t>
         </is>
       </c>
       <c r="C71">
@@ -1322,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Ixtlahuaca</t>
@@ -1335,9 +1655,14 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Naucalpan de Juárez</t>
+          <t>Naucalpan De Juárez</t>
         </is>
       </c>
       <c r="C73">
@@ -1348,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -1357,13 +1687,18 @@
         <v>6</v>
       </c>
       <c r="D74">
-        <v>0.009538950715421303</v>
+        <v>0.009538950715421305</v>
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>San Felipe del Progreso</t>
+          <t>San Felipe Del Progreso</t>
         </is>
       </c>
       <c r="C75">
@@ -1374,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Temascaltepec</t>
@@ -1387,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Tepotzotlán</t>
@@ -1400,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Tianguistenco</t>
@@ -1413,9 +1763,14 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C79">
@@ -1426,6 +1781,11 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -1439,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1470,9 +1835,14 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C83">
@@ -1483,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -1492,10 +1867,15 @@
         <v>6</v>
       </c>
       <c r="D84">
-        <v>0.009538950715421303</v>
+        <v>0.009538950715421305</v>
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Comonfort</t>
@@ -1509,9 +1889,14 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna de la Independencia Nacional</t>
+          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
         </is>
       </c>
       <c r="C86">
@@ -1522,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Guanajuato</t>
@@ -1535,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -1548,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>León</t>
@@ -1561,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -1574,9 +1979,14 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>San Luis de la Paz</t>
+          <t>San Luis De La Paz</t>
         </is>
       </c>
       <c r="C91">
@@ -1587,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1607,7 +2022,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C93">
@@ -1618,9 +2033,14 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ajuchitlán del Progreso</t>
+          <t>Ajuchitlán Del Progreso</t>
         </is>
       </c>
       <c r="C94">
@@ -1631,6 +2051,11 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>Arcelia</t>
@@ -1644,9 +2069,14 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C96">
@@ -1657,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Azoyú</t>
@@ -1670,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Copanatoyac</t>
@@ -1683,9 +2123,14 @@
       </c>
     </row>
     <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Coyuca de Benítez</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C99">
@@ -1696,9 +2141,14 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Coyuca de Catalán</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C100">
@@ -1709,9 +2159,14 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Cutzamala de Pinzón</t>
+          <t>Cutzamala De Pinzón</t>
         </is>
       </c>
       <c r="C101">
@@ -1722,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Quechultenango</t>
@@ -1735,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -1748,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>San Marcos</t>
@@ -1761,9 +2231,14 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Tlapa de Comonfort</t>
+          <t>Tlapa De Comonfort</t>
         </is>
       </c>
       <c r="C105">
@@ -1774,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Xalpatláhuac</t>
@@ -1787,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Xochihuehuetlán</t>
@@ -1800,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1831,9 +2321,14 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Molango de Escamilla</t>
+          <t>Molango De Escamilla</t>
         </is>
       </c>
       <c r="C110">
@@ -1844,9 +2339,14 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C111">
@@ -1857,6 +2357,11 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
           <t>Tepeapulco</t>
@@ -1870,9 +2375,14 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Tula de Allende</t>
+          <t>Tula De Allende</t>
         </is>
       </c>
       <c r="C113">
@@ -1883,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -1896,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1927,9 +2447,14 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C117">
@@ -1940,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Ayotlán</t>
@@ -1953,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Ayutla</t>
@@ -1966,9 +2501,14 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Concepción de Buenos Aires</t>
+          <t>Concepción De Buenos Aires</t>
         </is>
       </c>
       <c r="C120">
@@ -1979,9 +2519,14 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Cuautitlán de García Barragán</t>
+          <t>Cuautitlán De García Barragán</t>
         </is>
       </c>
       <c r="C121">
@@ -1992,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Cuquío</t>
@@ -2005,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -2018,9 +2573,14 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Ixtlahuacán de los Membrillos</t>
+          <t>Ixtlahuacán De Los Membrillos</t>
         </is>
       </c>
       <c r="C124">
@@ -2031,9 +2591,14 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Ixtlahuacán del Río</t>
+          <t>Ixtlahuacán Del Río</t>
         </is>
       </c>
       <c r="C125">
@@ -2044,6 +2609,11 @@
       </c>
     </row>
     <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>Jalostotitlán</t>
@@ -2057,9 +2627,14 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C127">
@@ -2070,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Ocotlán</t>
@@ -2083,9 +2663,14 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ojuelos de Jalisco</t>
+          <t>Ojuelos De Jalisco</t>
         </is>
       </c>
       <c r="C129">
@@ -2096,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>San Gabriel</t>
@@ -2109,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>San Marcos</t>
@@ -2122,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Tecalitlán</t>
@@ -2135,6 +2735,11 @@
       </c>
     </row>
     <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>Tecolotlán</t>
@@ -2148,9 +2753,14 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Teocuitatlán de Corona</t>
+          <t>Teocuitatlán De Corona</t>
         </is>
       </c>
       <c r="C134">
@@ -2161,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Teuchitlán</t>
@@ -2174,9 +2789,14 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Tizapán el Alto</t>
+          <t>Tizapán El Alto</t>
         </is>
       </c>
       <c r="C136">
@@ -2187,9 +2807,14 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Tlajomulco de Zúñiga</t>
+          <t>Tlajomulco De Zúñiga</t>
         </is>
       </c>
       <c r="C137">
@@ -2200,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Tomatlán</t>
@@ -2213,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Tuxcueca</t>
@@ -2226,9 +2861,14 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C140">
@@ -2239,6 +2879,11 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2270,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Contepec</t>
@@ -2283,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Gabriel Zamora</t>
@@ -2296,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Hidalgo</t>
@@ -2309,6 +2969,11 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>La Huacana</t>
@@ -2322,6 +2987,11 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -2335,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>Maravatío</t>
@@ -2348,6 +3023,11 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -2361,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Múgica</t>
@@ -2374,6 +3059,11 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>Pajacuarán</t>
@@ -2387,6 +3077,11 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>Pátzcuaro</t>
@@ -2400,6 +3095,11 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>Tocumbo</t>
@@ -2413,6 +3113,11 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -2426,6 +3131,11 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -2439,6 +3149,11 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -2452,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -2465,6 +3185,11 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2496,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Ayala</t>
@@ -2509,6 +3239,11 @@
       </c>
     </row>
     <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>Cuautla</t>
@@ -2522,6 +3257,11 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -2535,9 +3275,14 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Jonacatepec de Leandro Valle</t>
+          <t>Jonacatepec De Leandro Valle</t>
         </is>
       </c>
       <c r="C163">
@@ -2548,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Ocuituco</t>
@@ -2561,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2592,6 +3347,11 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>San Blas</t>
@@ -2605,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -2618,6 +3383,11 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2649,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2669,7 +3444,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Acatlán de Pérez Figueroa</t>
+          <t>Acatlán De Pérez Figueroa</t>
         </is>
       </c>
       <c r="C172">
@@ -2680,6 +3455,11 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>Cosolapa</t>
@@ -2693,9 +3473,14 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Ejutla de Crespo</t>
+          <t>Heroica Ciudad De Ejutla De Crespo</t>
         </is>
       </c>
       <c r="C174">
@@ -2706,9 +3491,14 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C175">
@@ -2719,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Loma Bonita</t>
@@ -2732,9 +3527,14 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C177">
@@ -2745,9 +3545,14 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Putla Villa de Guerrero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C178">
@@ -2758,6 +3563,11 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>San Agustín Chayuco</t>
@@ -2771,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>San Agustín Yatareni</t>
@@ -2784,6 +3599,11 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>San Andrés Huayápam</t>
@@ -2797,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>San Antonino Monte Verde</t>
@@ -2810,9 +3635,14 @@
       </c>
     </row>
     <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>San Dionisio del Mar</t>
+          <t>San Dionisio Del Mar</t>
         </is>
       </c>
       <c r="C183">
@@ -2823,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>San Ildefonso Villa Alta</t>
@@ -2836,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>San José Tenango</t>
@@ -2849,6 +3689,11 @@
       </c>
     </row>
     <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -2862,6 +3707,11 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>San Juan Guichicovi</t>
@@ -2875,6 +3725,11 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>San Martín Peras</t>
@@ -2888,6 +3743,11 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>San Miguel Panixtlahuaca</t>
@@ -2901,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Santa María Tlahuitoltepec</t>
@@ -2914,6 +3779,11 @@
       </c>
     </row>
     <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>Santa María Zacatepec</t>
@@ -2927,6 +3797,11 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>Santiago Chazumba</t>
@@ -2940,6 +3815,11 @@
       </c>
     </row>
     <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>Santiago Juxtlahuaca</t>
@@ -2953,6 +3833,11 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
           <t>Santiago Zacatepec</t>
@@ -2966,6 +3851,11 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>Santos Reyes Nopala</t>
@@ -2979,6 +3869,11 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>Zapotitlán Lagunas</t>
@@ -2992,6 +3887,11 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3023,6 +3923,11 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>Amozoc</t>
@@ -3036,6 +3941,11 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>Atlixco</t>
@@ -3049,6 +3959,11 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>Caltepec</t>
@@ -3062,6 +3977,11 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>Chapulco</t>
@@ -3075,6 +3995,11 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>Chiautla</t>
@@ -3088,6 +4013,11 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Chiautzingo</t>
@@ -3101,6 +4031,11 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>Chignahuapan</t>
@@ -3114,6 +4049,11 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>Chignautla</t>
@@ -3127,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Chinantla</t>
@@ -3140,6 +4085,11 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>Coronango</t>
@@ -3153,6 +4103,11 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -3166,6 +4121,11 @@
       </c>
     </row>
     <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>Huejotzingo</t>
@@ -3179,9 +4139,14 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C211">
@@ -3192,6 +4157,11 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>Jolalpan</t>
@@ -3205,6 +4175,11 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>Juan N. Méndez</t>
@@ -3218,6 +4193,11 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>Nealtican</t>
@@ -3231,6 +4211,11 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>Piaxtla</t>
@@ -3244,6 +4229,11 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -3257,6 +4247,11 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>San Andrés Cholula</t>
@@ -3270,6 +4265,11 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>San Felipe Teotlalcingo</t>
@@ -3283,6 +4283,11 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>San Juan Atenco</t>
@@ -3296,6 +4301,11 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>San Martín Texmelucan</t>
@@ -3309,6 +4319,11 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>Tenampulco</t>
@@ -3322,6 +4337,11 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Teotlalco</t>
@@ -3335,6 +4355,11 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -3348,6 +4373,11 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>Tepexco</t>
@@ -3361,9 +4391,14 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Tepexi de Rodríguez</t>
+          <t>Tepexi De Rodríguez</t>
         </is>
       </c>
       <c r="C225">
@@ -3374,6 +4409,11 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>Tianguismanalco</t>
@@ -3387,9 +4427,14 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C227">
@@ -3400,6 +4445,11 @@
       </c>
     </row>
     <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>Tlahuapan</t>
@@ -3413,6 +4463,11 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>Tlatlauquitepec</t>
@@ -3426,6 +4481,11 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>Tochimilco</t>
@@ -3439,6 +4499,11 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>Tulcingo</t>
@@ -3452,6 +4517,11 @@
       </c>
     </row>
     <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -3465,6 +4535,11 @@
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -3478,6 +4553,11 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3509,6 +4589,11 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -3522,6 +4607,11 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3553,6 +4643,11 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Quintana Roo</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3584,6 +4679,11 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>Rioverde</t>
@@ -3597,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>Salinas</t>
@@ -3610,6 +4715,11 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -3623,9 +4733,14 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Santa María del Río</t>
+          <t>Santa María Del Río</t>
         </is>
       </c>
       <c r="C244">
@@ -3636,6 +4751,11 @@
       </c>
     </row>
     <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>Venado</t>
@@ -3649,19 +4769,29 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Villa de Reyes</t>
+          <t>Villa De Reyes</t>
         </is>
       </c>
       <c r="C246">
         <v>6</v>
       </c>
       <c r="D246">
-        <v>0.009538950715421303</v>
+        <v>0.009538950715421305</v>
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3693,6 +4823,11 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
           <t>Elota</t>
@@ -3706,6 +4841,11 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>Guasave</t>
@@ -3719,6 +4859,11 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3750,6 +4895,11 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>Cajeme</t>
@@ -3763,6 +4913,11 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>Empalme</t>
@@ -3776,6 +4931,11 @@
       </c>
     </row>
     <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>Hermosillo</t>
@@ -3789,6 +4949,11 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>Navojoa</t>
@@ -3802,6 +4967,11 @@
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3833,6 +5003,11 @@
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
           <t>Cunduacán</t>
@@ -3846,6 +5021,11 @@
       </c>
     </row>
     <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B260" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3877,6 +5057,11 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -3890,6 +5075,11 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
           <t>San Fernando</t>
@@ -3903,6 +5093,11 @@
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -3916,6 +5111,11 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3925,7 +5125,7 @@
         <v>6</v>
       </c>
       <c r="D265">
-        <v>0.009538950715421303</v>
+        <v>0.009538950715421305</v>
       </c>
     </row>
     <row r="266">
@@ -3936,7 +5136,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Contla de Juan Cuamatzi</t>
+          <t>Contla De Juan Cuamatzi</t>
         </is>
       </c>
       <c r="C266">
@@ -3947,6 +5147,11 @@
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
           <t>Ixtenco</t>
@@ -3960,6 +5165,11 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
           <t>Santa Cruz Tlaxcala</t>
@@ -3973,6 +5183,11 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -3986,6 +5201,11 @@
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
           <t>Zacatelco</t>
@@ -3999,6 +5219,11 @@
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4030,9 +5255,14 @@
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Camarón de Tejeda</t>
+          <t>Camarón De Tejeda</t>
         </is>
       </c>
       <c r="C273">
@@ -4043,6 +5273,11 @@
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
           <t>Coatzacoalcos</t>
@@ -4056,6 +5291,11 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -4069,6 +5309,11 @@
       </c>
     </row>
     <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -4082,9 +5327,14 @@
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Ignacio de la Llave</t>
+          <t>Ignacio De La Llave</t>
         </is>
       </c>
       <c r="C277">
@@ -4095,9 +5345,14 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Ixhuatlán de Madero</t>
+          <t>Ixhuatlán De Madero</t>
         </is>
       </c>
       <c r="C278">
@@ -4108,6 +5363,11 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>José Azueta</t>
@@ -4121,6 +5381,11 @@
       </c>
     </row>
     <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
           <t>La Antigua</t>
@@ -4134,6 +5399,11 @@
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
           <t>Las Choapas</t>
@@ -4147,6 +5417,11 @@
       </c>
     </row>
     <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B282" t="inlineStr">
         <is>
           <t>Manlio Fabio Altamirano</t>
@@ -4160,9 +5435,14 @@
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C283">
@@ -4173,6 +5453,11 @@
       </c>
     </row>
     <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
           <t>Minatitlán</t>
@@ -4186,6 +5471,11 @@
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
           <t>Omealca</t>
@@ -4199,6 +5489,11 @@
       </c>
     </row>
     <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
           <t>Pánuco</t>
@@ -4212,6 +5507,11 @@
       </c>
     </row>
     <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B287" t="inlineStr">
         <is>
           <t>Papantla</t>
@@ -4225,9 +5525,14 @@
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Paso de Ovejas</t>
+          <t>Paso De Ovejas</t>
         </is>
       </c>
       <c r="C288">
@@ -4238,6 +5543,11 @@
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
           <t>Río Blanco</t>
@@ -4251,9 +5561,14 @@
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Sayula de Alemán</t>
+          <t>Sayula De Alemán</t>
         </is>
       </c>
       <c r="C290">
@@ -4264,9 +5579,14 @@
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Soledad de Doblado</t>
+          <t>Soledad De Doblado</t>
         </is>
       </c>
       <c r="C291">
@@ -4277,6 +5597,11 @@
       </c>
     </row>
     <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
           <t>Álamo Temapache</t>
@@ -4290,6 +5615,11 @@
       </c>
     </row>
     <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
           <t>Tierra Blanca</t>
@@ -4303,6 +5633,11 @@
       </c>
     </row>
     <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B294" t="inlineStr">
         <is>
           <t>Tlalixcoyan</t>
@@ -4316,6 +5651,11 @@
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -4329,6 +5669,11 @@
       </c>
     </row>
     <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
           <t>Yecuatla</t>
@@ -4342,6 +5687,11 @@
       </c>
     </row>
     <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
           <t>Zentla</t>
@@ -4355,6 +5705,11 @@
       </c>
     </row>
     <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4386,6 +5741,11 @@
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4417,9 +5777,14 @@
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Tlaltenango de Sánchez Román</t>
+          <t>Tlaltenango De Sánchez Román</t>
         </is>
       </c>
       <c r="C302">
@@ -4430,6 +5795,11 @@
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4453,41 +5823,6 @@
       </c>
       <c r="D304">
         <v>1</v>
-      </c>
-    </row>
-    <row r="306">
-      <c r="A306" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 794,748</t>
-        </is>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="309">
-      <c r="A309" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="310">
-      <c r="A310" t="inlineStr">
-        <is>
-          <t>Diciembre de 2019</t>
-        </is>
       </c>
     </row>
   </sheetData>
